--- a/03_Outputs/all/idx8_demografica_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx8_demografica_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>-0.1976854795682791</v>
+        <v>-0.1976854795682788</v>
       </c>
       <c r="D2">
-        <v>0.06092544138563031</v>
+        <v>0.06092544138563023</v>
       </c>
       <c r="E2">
         <v>6.1</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.1579166445736203</v>
+        <v>0.1579166445736204</v>
       </c>
       <c r="D3">
-        <v>0.04866893255790419</v>
+        <v>0.04866893255790421</v>
       </c>
       <c r="E3">
         <v>4.9</v>
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.354424493824064</v>
+        <v>0.3544244938240639</v>
       </c>
       <c r="D4">
         <v>0.1092314355675854</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.3458684211341021</v>
+        <v>0.3458684211341022</v>
       </c>
       <c r="D7">
         <v>0.1065945069155576</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.2517544859870865</v>
+        <v>0.2517544859870866</v>
       </c>
       <c r="D8">
-        <v>0.07758917454672237</v>
+        <v>0.07758917454672239</v>
       </c>
       <c r="E8">
         <v>7.8</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.314028751964716</v>
+        <v>0.3140287519647158</v>
       </c>
       <c r="D9">
-        <v>0.09678171792390435</v>
+        <v>0.09678171792390429</v>
       </c>
       <c r="E9">
         <v>9.699999999999999</v>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.3271144115333573</v>
+        <v>0.3271144115333574</v>
       </c>
       <c r="D12">
         <v>0.1008146372196597</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.2100351908705056</v>
+        <v>0.2100351908705047</v>
       </c>
       <c r="D13">
-        <v>0.07413833150902191</v>
+        <v>0.07413833150902158</v>
       </c>
       <c r="E13">
         <v>7.4</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.4770548317804415</v>
+        <v>0.4770548317804416</v>
       </c>
       <c r="D14">
         <v>0.1683910639923419</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>0.0733132385520306</v>
+        <v>0.07331323855203092</v>
       </c>
       <c r="D15">
-        <v>0.02587814528243282</v>
+        <v>0.02587814528243292</v>
       </c>
       <c r="E15">
         <v>2.6</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.1445853002927382</v>
+        <v>-0.1445853002927378</v>
       </c>
       <c r="D16">
-        <v>0.05103579490659427</v>
+        <v>0.05103579490659414</v>
       </c>
       <c r="E16">
         <v>5.1</v>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.2942445687784357</v>
+        <v>0.2942445687784358</v>
       </c>
       <c r="D17">
         <v>0.1038626017593142</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.1242933894611006</v>
+        <v>-0.1242933894611009</v>
       </c>
       <c r="D18">
-        <v>0.04387314560981531</v>
+        <v>0.04387314560981541</v>
       </c>
       <c r="E18">
         <v>4.4</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.5349447412080018</v>
+        <v>-0.5349447412080024</v>
       </c>
       <c r="D19">
-        <v>0.188825074494962</v>
+        <v>0.1888250744949621</v>
       </c>
       <c r="E19">
         <v>18.9</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.0113680370768881</v>
+        <v>-0.01136803707688819</v>
       </c>
       <c r="D21">
-        <v>0.004012695672187641</v>
+        <v>0.004012695672187669</v>
       </c>
       <c r="E21">
         <v>0.4</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.3746458911462081</v>
+        <v>-0.3746458911462084</v>
       </c>
       <c r="D22">
-        <v>0.1322427025736616</v>
+        <v>0.1322427025736617</v>
       </c>
       <c r="E22">
         <v>13.2</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.3030882395978312</v>
+        <v>0.3030882395978315</v>
       </c>
       <c r="D23">
-        <v>0.106984245309843</v>
+        <v>0.1069842453098431</v>
       </c>
       <c r="E23">
         <v>10.7</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.8357515526508794</v>
+        <v>-0.8357515526508805</v>
       </c>
       <c r="D24">
-        <v>0.4004213494538162</v>
+        <v>0.4004213494538168</v>
       </c>
       <c r="E24">
         <v>40</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.4529652463263221</v>
+        <v>0.4529652463263201</v>
       </c>
       <c r="D25">
-        <v>0.2170225764036758</v>
+        <v>0.2170225764036749</v>
       </c>
       <c r="E25">
         <v>21.7</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>-0.0711964300227491</v>
+        <v>-0.07119643002274868</v>
       </c>
       <c r="D26">
-        <v>0.03411129838237027</v>
+        <v>0.03411129838237009</v>
       </c>
       <c r="E26">
         <v>3.4</v>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.1240042152930118</v>
+        <v>-0.1240042152930129</v>
       </c>
       <c r="D27">
-        <v>0.05941231585881528</v>
+        <v>0.05941231585881585</v>
       </c>
       <c r="E27">
         <v>5.9</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.1925822619849016</v>
+        <v>-0.1925822619849011</v>
       </c>
       <c r="D28">
-        <v>0.09226910674621948</v>
+        <v>0.09226910674621926</v>
       </c>
       <c r="E28">
         <v>9.199999999999999</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.02631815201427266</v>
+        <v>0.02631815201427308</v>
       </c>
       <c r="D29">
-        <v>0.01260942909559624</v>
+        <v>0.01260942909559644</v>
       </c>
       <c r="E29">
         <v>1.3</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>-0.04701297652228</v>
+        <v>-0.04701297652228005</v>
       </c>
       <c r="D30">
-        <v>0.02252463598922651</v>
+        <v>0.02252463598922654</v>
       </c>
       <c r="E30">
         <v>2.3</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.04568784288805169</v>
+        <v>-0.04568784288805128</v>
       </c>
       <c r="D31">
-        <v>0.02188974420070238</v>
+        <v>0.02188974420070219</v>
       </c>
       <c r="E31">
         <v>2.2</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.04242203896698608</v>
+        <v>-0.04242203896698599</v>
       </c>
       <c r="D32">
-        <v>0.02032504760040671</v>
+        <v>0.02032504760040667</v>
       </c>
       <c r="E32">
         <v>2</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>-0.1027352710340119</v>
+        <v>-0.1027352710340121</v>
       </c>
       <c r="D33">
-        <v>0.04922203941286248</v>
+        <v>0.04922203941286258</v>
       </c>
       <c r="E33">
         <v>4.9</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.146504313224203</v>
+        <v>-0.1465043132242028</v>
       </c>
       <c r="D34">
-        <v>0.07019245685630877</v>
+        <v>0.07019245685630872</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.3364621712430025</v>
+        <v>-0.3364621712430005</v>
       </c>
       <c r="D35">
-        <v>0.1258439059194373</v>
+        <v>0.1258439059194366</v>
       </c>
       <c r="E35">
         <v>12.6</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.6425677767482388</v>
+        <v>-0.6425677767482401</v>
       </c>
       <c r="D36">
-        <v>0.2403338198324995</v>
+        <v>0.2403338198325001</v>
       </c>
       <c r="E36">
         <v>24</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.0283071637078367</v>
+        <v>-0.02830716370783626</v>
       </c>
       <c r="D37">
-        <v>0.01058747268180211</v>
+        <v>0.01058747268180195</v>
       </c>
       <c r="E37">
         <v>1.1</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.4565702679386475</v>
+        <v>-0.4565702679386469</v>
       </c>
       <c r="D38">
-        <v>0.1707668521302701</v>
+        <v>0.17076685213027</v>
       </c>
       <c r="E38">
         <v>17.1</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.1890382791879423</v>
+        <v>0.1890382791879431</v>
       </c>
       <c r="D39">
-        <v>0.07070427957298776</v>
+        <v>0.0707042795729881</v>
       </c>
       <c r="E39">
         <v>7.1</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.1446156902418864</v>
+        <v>0.1446156902418862</v>
       </c>
       <c r="D40">
-        <v>0.05408929999482946</v>
+        <v>0.0540892999948294</v>
       </c>
       <c r="E40">
         <v>5.4</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.04568746193835038</v>
+        <v>-0.04568746193835035</v>
       </c>
       <c r="D41">
         <v>0.01708806859513248</v>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.256553695698145</v>
+        <v>0.2565536956981445</v>
       </c>
       <c r="D42">
-        <v>0.09595646079750118</v>
+        <v>0.09595646079750107</v>
       </c>
       <c r="E42">
         <v>9.6</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.05290805235963709</v>
+        <v>0.0529080523596373</v>
       </c>
       <c r="D43">
-        <v>0.01978872079119446</v>
+        <v>0.01978872079119455</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.2887456930812249</v>
+        <v>-0.2887456930812243</v>
       </c>
       <c r="D44">
-        <v>0.1079969427187488</v>
+        <v>0.1079969427187486</v>
       </c>
       <c r="E44">
         <v>10.8</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.2321906661126853</v>
+        <v>0.2321906661126859</v>
       </c>
       <c r="D45">
-        <v>0.08684417696559682</v>
+        <v>0.08684417696559707</v>
       </c>
       <c r="E45">
         <v>8.699999999999999</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="C46">
-        <v>-0.2628050073112407</v>
+        <v>-0.2628050073112405</v>
       </c>
       <c r="D46">
-        <v>0.1095925325290464</v>
+        <v>0.1095925325290462</v>
       </c>
       <c r="E46">
         <v>11</v>
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.3572789928494972</v>
+        <v>-0.3572789928494975</v>
       </c>
       <c r="D47">
         <v>0.1489892070413709</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.1896659038333229</v>
+        <v>0.1896659038333241</v>
       </c>
       <c r="D48">
-        <v>0.07909273475481213</v>
+        <v>0.07909273475481253</v>
       </c>
       <c r="E48">
         <v>7.9</v>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.5930531347727174</v>
+        <v>0.5930531347727173</v>
       </c>
       <c r="D49">
-        <v>0.2473095761339857</v>
+        <v>0.2473095761339854</v>
       </c>
       <c r="E49">
         <v>24.7</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.01379707030469641</v>
+        <v>-0.01379707030469525</v>
       </c>
       <c r="D50">
-        <v>0.005753527650187613</v>
+        <v>0.005753527650187122</v>
       </c>
       <c r="E50">
         <v>0.6</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.2038069852100205</v>
+        <v>-0.2038069852100213</v>
       </c>
       <c r="D51">
-        <v>0.08498971874544148</v>
+        <v>0.08498971874544176</v>
       </c>
       <c r="E51">
         <v>8.5</v>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.6028306014029142</v>
+        <v>-0.6028306014029139</v>
       </c>
       <c r="D52">
-        <v>0.2513868855455696</v>
+        <v>0.2513868855455693</v>
       </c>
       <c r="E52">
         <v>25.1</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C53">
-        <v>-0.08954076214994729</v>
+        <v>-0.08954076214994898</v>
       </c>
       <c r="D53">
-        <v>0.03733946696446366</v>
+        <v>0.03733946696446432</v>
       </c>
       <c r="E53">
         <v>3.7</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.02557381578928297</v>
+        <v>0.02557381578928283</v>
       </c>
       <c r="D54">
-        <v>0.01066455798332483</v>
+        <v>0.01066455798332477</v>
       </c>
       <c r="E54">
         <v>1.1</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.03266622855123858</v>
+        <v>0.03266622855123866</v>
       </c>
       <c r="D55">
-        <v>0.01362217087006681</v>
+        <v>0.01362217087006683</v>
       </c>
       <c r="E55">
         <v>1.4</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C56">
-        <v>-0.02700079025808947</v>
+        <v>-0.0270007902580893</v>
       </c>
       <c r="D56">
-        <v>0.01125962178173103</v>
+        <v>0.01125962178173095</v>
       </c>
       <c r="E56">
         <v>1.1</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.1046964959308907</v>
+        <v>0.1046964959308894</v>
       </c>
       <c r="D57">
-        <v>0.04188157971228258</v>
+        <v>0.04188157971228209</v>
       </c>
       <c r="E57">
         <v>4.2</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="C58">
-        <v>-0.02105028142943397</v>
+        <v>-0.02105028142943481</v>
       </c>
       <c r="D58">
-        <v>0.008420712000091868</v>
+        <v>0.008420712000092204</v>
       </c>
       <c r="E58">
         <v>0.8</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>-0.3277527492060134</v>
+        <v>-0.3277527492060129</v>
       </c>
       <c r="D59">
-        <v>0.1311104327775436</v>
+        <v>0.1311104327775434</v>
       </c>
       <c r="E59">
         <v>13.1</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.1805661219766577</v>
+        <v>0.1805661219766586</v>
       </c>
       <c r="D60">
-        <v>0.07223159059587826</v>
+        <v>0.07223159059587862</v>
       </c>
       <c r="E60">
         <v>7.2</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.5137894798103285</v>
+        <v>-0.5137894798103286</v>
       </c>
       <c r="D61">
         <v>0.2055304226056672</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.3562714496350019</v>
+        <v>0.3562714496350014</v>
       </c>
       <c r="D62">
-        <v>0.1425187250483357</v>
+        <v>0.1425187250483355</v>
       </c>
       <c r="E62">
         <v>14.3</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="C63">
-        <v>-0.1609599733511454</v>
+        <v>-0.1609599733511463</v>
       </c>
       <c r="D63">
-        <v>0.06438857284051538</v>
+        <v>0.06438857284051573</v>
       </c>
       <c r="E63">
         <v>6.4</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.6476027276424153</v>
+        <v>0.6476027276424152</v>
       </c>
       <c r="D64">
         <v>0.2590595322077529</v>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="C65">
-        <v>-0.07106217286495885</v>
+        <v>-0.07106217286495876</v>
       </c>
       <c r="D65">
-        <v>0.02842689271412046</v>
+        <v>0.02842689271412042</v>
       </c>
       <c r="E65">
         <v>2.8</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.04104799946188972</v>
+        <v>0.0410479994618891</v>
       </c>
       <c r="D66">
-        <v>0.01642036866857194</v>
+        <v>0.01642036866857169</v>
       </c>
       <c r="E66">
         <v>1.6</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="C67">
-        <v>-0.07502258621069532</v>
+        <v>-0.07502258621069527</v>
       </c>
       <c r="D67">
-        <v>0.03001117082924036</v>
+        <v>0.03001117082924034</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>-0.1491129545081732</v>
+        <v>-0.1491129545081731</v>
       </c>
       <c r="D68">
-        <v>0.05276422929932165</v>
+        <v>0.0527642292993217</v>
       </c>
       <c r="E68">
         <v>5.3</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.0209192267261427</v>
+        <v>-0.02091922672614245</v>
       </c>
       <c r="D69">
-        <v>0.007402354003267975</v>
+        <v>0.007402354003267895</v>
       </c>
       <c r="E69">
         <v>0.7</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.2144237840868556</v>
+        <v>-0.2144237840868548</v>
       </c>
       <c r="D70">
-        <v>0.07587473367491318</v>
+        <v>0.07587473367491297</v>
       </c>
       <c r="E70">
         <v>7.6</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="C71">
-        <v>0.1477955498349802</v>
+        <v>0.1477955498349797</v>
       </c>
       <c r="D71">
-        <v>0.05229806026333395</v>
+        <v>0.05229806026333384</v>
       </c>
       <c r="E71">
         <v>5.2</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.149108782451519</v>
+        <v>0.1491087824515187</v>
       </c>
       <c r="D72">
-        <v>0.05276275299999759</v>
+        <v>0.05276275299999753</v>
       </c>
       <c r="E72">
         <v>5.3</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="C73">
-        <v>-0.6199835414608659</v>
+        <v>-0.6199835414608653</v>
       </c>
       <c r="D73">
         <v>0.2193837138519951</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.2876175864213267</v>
+        <v>0.2876175864213262</v>
       </c>
       <c r="D74">
         <v>0.1017746602265903</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="C75">
-        <v>0.3725511589336267</v>
+        <v>0.3725511589336261</v>
       </c>
       <c r="D75">
-        <v>0.1318287525087195</v>
+        <v>0.1318287525087194</v>
       </c>
       <c r="E75">
         <v>13.2</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="C76">
-        <v>-0.4323941136483863</v>
+        <v>-0.4323941136483866</v>
       </c>
       <c r="D76">
-        <v>0.1530044269826997</v>
+        <v>0.1530044269826999</v>
       </c>
       <c r="E76">
         <v>15.3</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.1931650784508235</v>
+        <v>0.1931650784508241</v>
       </c>
       <c r="D77">
-        <v>0.06835225366983157</v>
+        <v>0.06835225366983186</v>
       </c>
       <c r="E77">
         <v>6.8</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.2389517717846793</v>
+        <v>0.2389517717846795</v>
       </c>
       <c r="D78">
-        <v>0.08455406251932941</v>
+        <v>0.08455406251932958</v>
       </c>
       <c r="E78">
         <v>8.5</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="C79">
-        <v>-0.0521442474295471</v>
+        <v>-0.05214424742954705</v>
       </c>
       <c r="D79">
-        <v>0.01976724898575236</v>
+        <v>0.01976724898575234</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.02421280492235832</v>
+        <v>0.02421280492235849</v>
       </c>
       <c r="D80">
-        <v>0.009178779388663707</v>
+        <v>0.009178779388663766</v>
       </c>
       <c r="E80">
         <v>0.9</v>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.6143540955015695</v>
+        <v>-0.6143540955015697</v>
       </c>
       <c r="D81">
         <v>0.2328941536188489</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.166325743704712</v>
+        <v>0.1663257437047122</v>
       </c>
       <c r="D82">
-        <v>0.06305206327876678</v>
+        <v>0.06305206327876683</v>
       </c>
       <c r="E82">
         <v>6.3</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="C83">
-        <v>0.4851110747203451</v>
+        <v>0.4851110747203439</v>
       </c>
       <c r="D83">
-        <v>0.1838996988632207</v>
+        <v>0.1838996988632201</v>
       </c>
       <c r="E83">
         <v>18.4</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="C84">
-        <v>0.4173356896234335</v>
+        <v>0.417335689623434</v>
       </c>
       <c r="D84">
-        <v>0.158206876004361</v>
+        <v>0.1582068760043611</v>
       </c>
       <c r="E84">
         <v>15.8</v>
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="C85">
-        <v>-0.1425606620711425</v>
+        <v>-0.1425606620711419</v>
       </c>
       <c r="D85">
-        <v>0.05404301033477305</v>
+        <v>0.05404301033477279</v>
       </c>
       <c r="E85">
         <v>5.4</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="C86">
-        <v>-0.2574455786061269</v>
+        <v>-0.2574455786061273</v>
       </c>
       <c r="D86">
-        <v>0.0975944826793062</v>
+        <v>0.09759448267930633</v>
       </c>
       <c r="E86">
         <v>9.800000000000001</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="C87">
-        <v>-0.2670150877644415</v>
+        <v>-0.2670150877644423</v>
       </c>
       <c r="D87">
-        <v>0.1012221670266433</v>
+        <v>0.1012221670266436</v>
       </c>
       <c r="E87">
         <v>10.1</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C88">
-        <v>0.1361379420939962</v>
+        <v>0.1361379420939955</v>
       </c>
       <c r="D88">
-        <v>0.05160823543221927</v>
+        <v>0.05160823543221898</v>
       </c>
       <c r="E88">
         <v>5.2</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.07526827036725975</v>
+        <v>0.07526827036726125</v>
       </c>
       <c r="D89">
-        <v>0.0285332843874447</v>
+        <v>0.02853328438744526</v>
       </c>
       <c r="E89">
         <v>2.9</v>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="C90">
-        <v>-0.009755604923258396</v>
+        <v>-0.009755604923258606</v>
       </c>
       <c r="D90">
-        <v>0.003704624520490165</v>
+        <v>0.003704624520490248</v>
       </c>
       <c r="E90">
         <v>0.4</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.0171357506721038</v>
+        <v>0.01713575067210409</v>
       </c>
       <c r="D91">
-        <v>0.006507184599648443</v>
+        <v>0.006507184599648557</v>
       </c>
       <c r="E91">
         <v>0.7</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="C92">
-        <v>-0.3552624356744028</v>
+        <v>-0.355262435674403</v>
       </c>
       <c r="D92">
-        <v>0.1349084901204535</v>
+        <v>0.1349084901204536</v>
       </c>
       <c r="E92">
         <v>13.5</v>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="C93">
-        <v>-0.0901667144264407</v>
+        <v>-0.09016671442643918</v>
       </c>
       <c r="D93">
-        <v>0.03424019564382466</v>
+        <v>0.03424019564382411</v>
       </c>
       <c r="E93">
         <v>3.4</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="C94">
-        <v>-0.3557443818823522</v>
+        <v>-0.3557443818823533</v>
       </c>
       <c r="D94">
-        <v>0.1350915059102042</v>
+        <v>0.1350915059102048</v>
       </c>
       <c r="E94">
         <v>13.5</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="C95">
-        <v>-0.1742158567424274</v>
+        <v>-0.1742158567424279</v>
       </c>
       <c r="D95">
-        <v>0.0661572849478033</v>
+        <v>0.06615728494780354</v>
       </c>
       <c r="E95">
         <v>6.6</v>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.1001320123220388</v>
+        <v>-0.1001320123220374</v>
       </c>
       <c r="D96">
-        <v>0.03802444964226264</v>
+        <v>0.03802444964226214</v>
       </c>
       <c r="E96">
         <v>3.8</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="C97">
-        <v>-0.2561040467766704</v>
+        <v>-0.2561040467766707</v>
       </c>
       <c r="D97">
-        <v>0.09725376734185359</v>
+        <v>0.09725376734185377</v>
       </c>
       <c r="E97">
         <v>9.699999999999999</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C98">
-        <v>0.4316510807749201</v>
+        <v>0.4316510807749211</v>
       </c>
       <c r="D98">
-        <v>0.1639165577854033</v>
+        <v>0.1639165577854038</v>
       </c>
       <c r="E98">
         <v>16.4</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="C99">
-        <v>0.2083574021142429</v>
+        <v>0.2083574021142402</v>
       </c>
       <c r="D99">
-        <v>0.07912230425176361</v>
+        <v>0.07912230425176263</v>
       </c>
       <c r="E99">
         <v>7.9</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.6348333359483891</v>
+        <v>0.6348333359483895</v>
       </c>
       <c r="D100">
-        <v>0.2410736352362924</v>
+        <v>0.2410736352362927</v>
       </c>
       <c r="E100">
         <v>24.1</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.001790713920036986</v>
+        <v>0.001790713920036441</v>
       </c>
       <c r="D101">
-        <v>0.0008142603540451112</v>
+        <v>0.0008142603540448658</v>
       </c>
       <c r="E101">
         <v>0.1</v>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="C102">
-        <v>-0.0004007077231938967</v>
+        <v>-0.0004007077231939287</v>
       </c>
       <c r="D102">
-        <v>0.0001822068890544692</v>
+        <v>0.0001822068890544843</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="C103">
-        <v>-0.09174144424838658</v>
+        <v>-0.09174144424838476</v>
       </c>
       <c r="D103">
-        <v>0.04171599943376671</v>
+        <v>0.04171599943376602</v>
       </c>
       <c r="E103">
         <v>4.2</v>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.463272205502625</v>
+        <v>0.4632722055026252</v>
       </c>
       <c r="D104">
-        <v>0.2106557534684466</v>
+        <v>0.2106557534684474</v>
       </c>
       <c r="E104">
         <v>21.1</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="C105">
-        <v>-0.1004828998622346</v>
+        <v>-0.1004828998622336</v>
       </c>
       <c r="D105">
-        <v>0.04569085028144117</v>
+        <v>0.04569085028144087</v>
       </c>
       <c r="E105">
         <v>4.6</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="C106">
-        <v>0.06233886421393246</v>
+        <v>0.06233886421393182</v>
       </c>
       <c r="D106">
-        <v>0.02834627300186416</v>
+        <v>0.02834627300186396</v>
       </c>
       <c r="E106">
         <v>2.8</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.3758706380381838</v>
+        <v>0.3758706380381847</v>
       </c>
       <c r="D107">
-        <v>0.1709131511066893</v>
+        <v>0.1709131511066903</v>
       </c>
       <c r="E107">
         <v>17.1</v>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="C108">
-        <v>-0.12207801119193</v>
+        <v>-0.1220780111919288</v>
       </c>
       <c r="D108">
-        <v>0.05551042157097366</v>
+        <v>0.05551042157097332</v>
       </c>
       <c r="E108">
         <v>5.6</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="C109">
-        <v>0.01294442632223326</v>
+        <v>0.01294442632223182</v>
       </c>
       <c r="D109">
-        <v>0.005885994988990096</v>
+        <v>0.005885994988989458</v>
       </c>
       <c r="E109">
         <v>0.6</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="C110">
-        <v>-0.7466734815238745</v>
+        <v>-0.7466734815238752</v>
       </c>
       <c r="D110">
-        <v>0.3395219116904883</v>
+        <v>0.3395219116904898</v>
       </c>
       <c r="E110">
         <v>34</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="C111">
-        <v>0.2215974573345096</v>
+        <v>0.221597457334507</v>
       </c>
       <c r="D111">
-        <v>0.1007631772142405</v>
+        <v>0.1007631772142397</v>
       </c>
       <c r="E111">
         <v>10.1</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="C112">
-        <v>-0.006190070593961628</v>
+        <v>-0.00619007059396204</v>
       </c>
       <c r="D112">
-        <v>0.002482513192369632</v>
+        <v>0.002482513192369796</v>
       </c>
       <c r="E112">
         <v>0.2</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.001047463741717301</v>
+        <v>-0.001047463741717104</v>
       </c>
       <c r="D113">
-        <v>0.0004200828597784772</v>
+        <v>0.0004200828597783977</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.4021278350731566</v>
+        <v>-0.4021278350731577</v>
       </c>
       <c r="D114">
-        <v>0.1612724185346083</v>
+        <v>0.1612724185346086</v>
       </c>
       <c r="E114">
         <v>16.1</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="C115">
-        <v>0.07104110866158754</v>
+        <v>0.07104110866158798</v>
       </c>
       <c r="D115">
-        <v>0.02849086884808617</v>
+        <v>0.02849086884808633</v>
       </c>
       <c r="E115">
         <v>2.8</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="C116">
-        <v>0.284071905918608</v>
+        <v>0.284071905918609</v>
       </c>
       <c r="D116">
-        <v>0.1139263669646125</v>
+        <v>0.1139263669646128</v>
       </c>
       <c r="E116">
         <v>11.4</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="C117">
-        <v>-0.2864738108722374</v>
+        <v>-0.2864738108722373</v>
       </c>
       <c r="D117">
         <v>0.11488964527359</v>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="C118">
-        <v>0.04990808221665699</v>
+        <v>0.04990808221665691</v>
       </c>
       <c r="D118">
-        <v>0.02001551850306527</v>
+        <v>0.02001551850306523</v>
       </c>
       <c r="E118">
         <v>2</v>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.1975567986299716</v>
+        <v>0.1975567986299718</v>
       </c>
       <c r="D119">
-        <v>0.07922968751271331</v>
+        <v>0.07922968751271334</v>
       </c>
       <c r="E119">
         <v>7.9</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.6439125769766368</v>
+        <v>0.6439125769766357</v>
       </c>
       <c r="D120">
-        <v>0.2582396182422498</v>
+        <v>0.2582396182422492</v>
       </c>
       <c r="E120">
         <v>25.8</v>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="C121">
-        <v>-0.09890285961275169</v>
+        <v>-0.09890285961275123</v>
       </c>
       <c r="D121">
-        <v>0.03966475826483277</v>
+        <v>0.03966475826483256</v>
       </c>
       <c r="E121">
         <v>4</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.4522368529361869</v>
+        <v>-0.452236852936187</v>
       </c>
       <c r="D122">
-        <v>0.1813685218040938</v>
+        <v>0.1813685218040937</v>
       </c>
       <c r="E122">
         <v>18.1</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1302426026692694</v>
+        <v>0.1302426026692693</v>
       </c>
     </row>
     <row r="4">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.07019224573949691</v>
+        <v>0.07019224573949683</v>
       </c>
     </row>
     <row r="5">
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.06439484468357057</v>
+        <v>0.06439484468357061</v>
       </c>
     </row>
     <row r="6">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.02454960805166463</v>
+        <v>0.02454960805166465</v>
       </c>
     </row>
     <row r="7">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.004857387453141079</v>
+        <v>0.004857387453141071</v>
       </c>
     </row>
     <row r="9">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.001409909310310624</v>
+        <v>0.001409909310310622</v>
       </c>
     </row>
     <row r="10">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.00011118651245809</v>
+        <v>0.0001111865124580902</v>
       </c>
     </row>
     <row r="11">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>3.453382790922755E-05</v>
+        <v>3.45338279092276E-05</v>
       </c>
     </row>
     <row r="12">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.105404342623154E-06</v>
+        <v>5.105404342623117E-06</v>
       </c>
     </row>
   </sheetData>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.354424493824064</v>
+        <v>0.3544244938240639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.3458684211341021</v>
+        <v>0.3458684211341022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3271144115333573</v>
+        <v>0.3271144115333574</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.314028751964716</v>
+        <v>0.3140287519647158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.2517544859870865</v>
+        <v>0.2517544859870866</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.1976854795682791</v>
+        <v>-0.1976854795682788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.5349447412080018</v>
+        <v>-0.5349447412080024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.4770548317804415</v>
+        <v>0.4770548317804416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.3746458911462081</v>
+        <v>-0.3746458911462084</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3030882395978312</v>
+        <v>0.3030882395978315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2942445687784357</v>
+        <v>0.2942445687784358</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.2100351908705056</v>
+        <v>0.2100351908705047</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.1445853002927382</v>
+        <v>-0.1445853002927378</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.1242933894611006</v>
+        <v>-0.1242933894611009</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.0733132385520306</v>
+        <v>0.07331323855203092</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/03_Outputs/all/idx8_demografica_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx8_demografica_loadings_y_tops.xlsx
@@ -471,7 +471,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1626,7 +1626,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1689,7 +1689,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2319,7 +2319,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2382,7 +2382,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2445,7 +2445,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2550,7 +2550,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2676,7 +2676,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2844,7 +2844,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2907,7 +2907,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3132,7 +3132,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B5">
@@ -3147,7 +3147,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B6">
@@ -3162,7 +3162,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B7">
@@ -3309,7 +3309,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ide_t_r</t>
+          <t>Índice dep. econ. (rural)</t>
         </is>
       </c>
       <c r="B5">
@@ -3324,7 +3324,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ide_h_r</t>
+          <t>Índice dep. econ. H (rural)</t>
         </is>
       </c>
       <c r="B6">
@@ -3339,7 +3339,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ide_m_r</t>
+          <t>Índice dep. econ. M (rural)</t>
         </is>
       </c>
       <c r="B7">
